--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_014/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_014/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -731,6 +736,41 @@
       </text>
     </comment>
     <comment ref="I6" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="I7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1378,12 +1418,12 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>RANS CFD to guide impeller trim decisions for P3-70 centrifugal pump near best efficiency point</t>
+          <t>RANS CFD predictions of pump head, efficiency, and diffuser performance to guide impeller/diffuser trim decisions near best efficiency point</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>Steady-state MRF RANS CFD (STAR-CCM+ 2022.1, SST k-omega) of the P3-70 single-stage centrifugal pump at 2900 rpm is used to predict head, efficiency, and diffuser loss at 0.6, 1.0, and 1.2 Q_BEP. The context of use is internal design guidance for trim decisions near BEP; stall-margin and off-BEP predictions are explicitly flagged as not ready for sign-off.</t>
+          <t>Steady-state MRF RANS CFD (STAR-CCM+ 2022.1, SST k-ω) of a P3-70 single-stage centrifugal pump at 7-blade impeller / 2-vane diffuser, 2900 rpm, for three operating points (0.6, 1.0, 1.2 Q_BEP). Model outputs (head, shaft power, diffuser pressure recovery) are compared against vendor acceptance-test data to support BEP-centric geometry trim decisions. Confidence at part-load (0.6 Q_BEP) is qualified; stall-margin predictions are not recommended for sign-off until identified issues are resolved.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1421,9 +1461,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2019,7 +2059,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>BEP Head and Efficiency Prediction Accuracy</t>
+          <t>BEP Trim Decision Accuracy Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2029,7 +2069,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>CFD predictions of head and efficiency at BEP must agree with laboratory acceptance test data within an acceptable tolerance to support trim decisions; the assessor targets approximately ±3% on head across the map, though this figure is disputed pending BC and temperature corrections.</t>
+          <t>CFD head and efficiency predictions must be within an acceptable band (targeting ~±3% on head) near BEP to reliably guide impeller/diffuser trim decisions; part-load predictions must be qualified with uncertainty bounds before use.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2051,13 +2091,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>STAR-CCM+ 2022.1 RANS MRF CFD Model</t>
+          <t>STAR-CCM+ RANS MRF Steady-State CFD Model</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Steady-state MRF RANS model with SST k-omega and curvature correction; poly+prism mesh (4.2M baseline); models P3-70 7-blade impeller and 2-vane diffuser at 2900 rpm.</t>
+          <t>Poly+prism-layer mesh (4.2M baseline), SST k-ω with curvature correction, MRF rotating reference frame, steady-state RANS model of P3-70 centrifugal pump at 2900 rpm.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2071,13 +2111,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>P3-70 Laboratory Acceptance Test Data</t>
+          <t>Vendor Acceptance Test Data</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Vendor acceptance test measurements of head and efficiency across the pump curve; conducted at 30-32 C water (viscosity 0.75-0.80 mPa·s), providing reference comparator values at 0.6, 1.0, and 1.2 Q_BEP.</t>
+          <t>Pump performance map (head, efficiency vs. flow rate) measured at 30–32 °C water; used as the experimental comparator for CFD validation at BEP and part-load operating points.</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2091,13 +2131,13 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>P3-70 Geometry and Operating Parameters</t>
+          <t>Mesh Sensitivity Study Dataset</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>CAD geometry (fillets &lt;0.25 mm removed), vendor drawing tip clearance 0.30±0.05 mm, rotational speed 2900 rpm, water at 25 C used in CFD runs.</t>
+          <t>Three mesh levels (coarse 2.1M, baseline 4.2M, fine 8.5M cells) used to compute Grid Convergence Index (GCI) for head and efficiency at BEP and off-design conditions.</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2262,12 +2302,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>CFD predicted head and efficiency at BEP compared against laboratory test curve values.</t>
+          <t>CFD predicted head and shaft efficiency at best efficiency point compared against vendor acceptance-test measurements.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Vendor acceptance test at BEP</t>
+          <t>Vendor acceptance-test pump performance curve at BEP</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2277,12 +2317,12 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t>Combined GCI and turbulence model spread yielding ~3.2% band on head at BEP; parameter sensitivity to inlet turbulence intensity and tip clearance also quantified.</t>
+          <t>GCI plus turbulence-model spread combined into a total uncertainty band; test uncertainty noted as 4–5% on head</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>Head error -1.1% (17.7 m predicted vs 17.9 m test); efficiency error -0.8% (78.6% vs 79.2%)</t>
+          <t>Head error –1.1% (17.7 m vs 17.9 m); efficiency error –0.8% (78.6% vs 79.2%); combined GCI + model spread ~3.2% on head at BEP</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2294,7 +2334,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Off-BEP (0.6 Q_BEP) Comparison</t>
+          <t>Part-Load (0.6 Q_BEP) Head and Efficiency Comparison</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2305,12 +2345,12 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>CFD predicted head, efficiency, and diffuser static pressure recovery at 0.6 Q_BEP compared against test data; fluid temperature and viscosity mismatch between CFD (25 C) and test (30-32 C) noted.</t>
+          <t>CFD predicted head, efficiency, and diffuser static pressure recovery at 0.6 Q_BEP compared against vendor test data; fluid temperature and viscosity mismatch between CFD (25 °C) and test (30–32 °C) acknowledged.</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Vendor acceptance test at 0.6 Q_BEP</t>
+          <t>Vendor acceptance-test data at 0.6 Q_BEP; pressure-tap diffuser recovery measurements</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
@@ -2320,12 +2360,12 @@
       </c>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>Inlet turbulence sensitivity (3% to 10%) shifts head up to 2.4% at this condition; viscosity mismatch not corrected in baseline runs.</t>
+          <t>Turbulence-model spread (SST vs S-A); inlet turbulence intensity sensitivity (3–10%)</t>
         </is>
       </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>Efficiency error 6.5%; diffuser static pressure recovery 8-10% higher than rig; turbulence model spread on head 7.4% between SST and SA.</t>
+          <t>Efficiency error 6.5%; diffuser static pressure recovery 8–10% higher than rig; turbulence model spread on head 7.4% at this operating point; inlet TI sensitivity up to 2.4% on head</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2348,7 +2388,7 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Three-mesh GCI study (2.1M coarse, 4.2M baseline, 8.5M fine) using head at BEP as the primary metric; efficiency GCI also computed but reported inconsistently in summary materials.</t>
+          <t>Three-mesh GCI study using head at BEP as primary metric; coarse (2.1M) → baseline (4.2M) → fine (8.5M); GCI reported for head. Efficiency GCI at BEP separately noted as &lt;0.5% but not yet reconciled with off-design metrics.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
@@ -2368,7 +2408,7 @@
       </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>GCI 1.8% on head at BEP (coarse to baseline to fine); efficiency reported as &lt;0.5% at BEP only; off-design GCI not yet computed.</t>
+          <t>GCI 1.8% on head at BEP (coarse→baseline→fine); &lt;0.5% for efficiency at BEP only</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2391,12 +2431,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Comparison of SST k-omega, Spalart-Allmaras (coarse mesh), and Scale-Adaptive Simulation (SAS) at BEP and 0.6 Q_BEP to assess model-form uncertainty.</t>
+          <t>SST k-ω (baseline) compared against Spalart–Allmaras on coarse mesh and Scale-Adaptive Simulation (SAS) at BEP; model spread evaluated on head and diffuser loss coefficient.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>SST k-omega baseline results</t>
+          <t>SST k-ω baseline predictions</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2406,12 +2446,12 @@
       </c>
       <c r="G6" s="41" t="inlineStr">
         <is>
-          <t>Model-form spread across turbulence models</t>
+          <t>Multiple turbulence model comparison (SST, S-A, SAS)</t>
         </is>
       </c>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>SAS vs SST head difference 1.2% at BEP; SA vs SST head difference 7.4% at 0.6 Q_BEP; diffuser loss coefficient difference 12% between SA and SST at 0.6 Q_BEP.</t>
+          <t>S-A vs SST head difference 7.4% at 0.6 Q_BEP; diffuser loss coefficient difference 12%; SAS vs SST head difference 1.2% at BEP</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2421,14 +2461,43 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
-      <c r="A7" s="24" t="n"/>
-      <c r="B7" s="24" t="n"/>
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>Cross-Solver Spot Check (STAR-CCM+ vs Fluent)</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>ValidationResult</t>
+        </is>
+      </c>
       <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="25" t="n"/>
-      <c r="F7" s="33" t="n"/>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>Single BEP case re-run in Ansys Fluent 2023 R2 to check solver independence of pressure-rise prediction.</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="inlineStr">
+        <is>
+          <t>STAR-CCM+ 2022.1 BEP pressure-rise result</t>
+        </is>
+      </c>
+      <c r="F7" s="41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="G7" s="33" t="n"/>
-      <c r="H7" s="33" t="n"/>
+      <c r="H7" s="41" t="inlineStr">
+        <is>
+          <t>Pressure rise difference 0.6% at BEP</t>
+        </is>
+      </c>
+      <c r="I7" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
       <c r="A8" s="24" t="n"/>
@@ -2638,19 +2707,19 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA, version control, and regression testing.</t>
+          <t>Commercial solver with documented testing; version identified</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>STAR-CCM+ 2022.1 is a well-established commercial solver with implied vendor QA. A spot-check against Fluent 2023 R2 at BEP showed 0.6% pressure rise difference, providing limited cross-code verification. However, no explicit documentation of solver certification, regression test suite, or ISO quality process is cited in the report. Version is recorded. Case directories noted as not yet pushed to repository (stale link).</t>
+          <t>STAR-CCM+ 2022.1 is a commercially validated CFD code; version is explicitly identified. A cross-solver spot-check against Fluent 2023 R2 was performed (0.6% pressure difference at BEP), providing indirect evidence of solver correctness. No explicit reference to ISO quality certification, regression test suite, or formal SQA documentation is provided in the report.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2678,12 +2747,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Evidence the solver correctly solves governing equations, e.g. comparison to analytical solutions or benchmark problems.</t>
+          <t>Evidence code correctly solves governing equations; benchmark or analytical comparison</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Cross-code spot-check (STAR-CCM+ vs Fluent) at BEP gives 0.6% head difference, providing a limited benchmark comparison. No method of manufactured solutions or analytical benchmark is described. Energy balance defect &lt;0.3% at BEP and mass residuals are noted. This constitutes basic but not comprehensive numerical code verification.</t>
+          <t>Cross-solver comparison (STAR-CCM+ vs Fluent) at BEP provides a consistency check. Energy balance defect &lt;0.3% at BEP and mass residuals &lt;1e-5 for p, k, ω are documented. No comparison to analytical solutions, method of manufactured solutions, or formal benchmark problems is reported. Evidence is limited to internal consistency checks and a single inter-code comparison.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2711,12 +2780,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Formal mesh convergence study with GCI reported for all primary QoIs at all operating points.</t>
+          <t>GCI computed for all quantities of interest across all operating points; monotonic convergence confirmed; near-wall treatment consistent across mesh levels</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three-mesh GCI study performed (2.1M, 4.2M, 8.5M cells); GCI of 1.8% reported for head at BEP. However, GCI for head at off-design points is not yet computed, the summary slide inconsistently reported "&lt;0.5% grid effect" (applicable to efficiency at BEP only), near-wall treatment is not uniform across meshes (fine mesh uses automatic switching with scalable wall functions where y+&gt;11), and the report explicitly flags the need to reconcile and recompute with monotonic metrics and unified wall treatment.</t>
+          <t>Three-level GCI study was conducted (GCI 1.8% on head at BEP). However, the report identifies several deficiencies: (1) the "&lt;0.5% grid effect" statement applied to efficiency only, not head at off-design; (2) non-monotonic convergence suspected at 0.6 Q_BEP; (3) the fine mesh used automatic wall-function switching (y+&gt;11 in parts of diffuser) inconsistent with the viscous-sublayer target on coarser meshes; (4) GCI has not yet been recomputed with unified wall treatment. Report explicitly flags need to reconcile these issues.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2737,19 +2806,19 @@
         </is>
       </c>
       <c r="C8" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="41" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Residuals converged to defined targets; mass balance verified; convergence monitoring documented.</t>
+          <t>Residuals reach target thresholds; mass balance satisfied; convergence documented for all cases</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Residuals converged to &lt;1e-5 for p, k, and omega. Mass balance within 0.2% at BEP. The 0.6 Q_BEP case residual leveled at 1.6% for mass balance until rotating-frame under-relaxation was reduced, and this is documented. Energy defect &lt;0.3% at BEP. Convergence monitoring is described qualitatively; solver settings adjustments are noted.</t>
+          <t>Residuals &lt;1e-5 for pressure, k, and ω are reported for converged cases. Mass balance within 0.2% for most cases. The 0.6 Q_BEP case initially leveled at 1.6% mass residual; corrective action (reducing rotating-frame under-relaxation) is documented. Energy defect &lt;0.3% at BEP provides additional confirmation of solver convergence quality.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2777,12 +2846,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review of model setup; boundary conditions verified and logged; mesh quality documented; post-processing validated.</t>
+          <t>Independent review of model setup; boundary conditions consistently documented; configuration log complete</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Multiple setup errors and inconsistencies are explicitly identified by the assessor: (1) boundary condition type was switched from mass-flow to fixed outlet static pressure for the BEP calibration run but not reflected in the config log; (2) near-wall treatment is non-uniform on the fine mesh; (3) the "within 2% across the map" summary claim bundled only head and omitted efficiency at off-BEP; (4) the GCI summary statement was inconsistent across documents; (5) case directories not yet in repository (stale link). No independent review is documented.</t>
+          <t>The report identifies multiple setup errors and inconsistencies: (1) the BEP calibration run used fixed outlet static pressure instead of mass-flow BC, but this was not reflected in the configuration log; (2) the case directory link in the slide deck is stale; (3) the "±3% everywhere" figure inadvertently double-counted test uncertainty in one variant and ignored it in another; (4) the inlet BC type flip was not formally reviewed. No evidence of independent model-setup review or formal use-error checklist is present. These are explicitly flagged as needing cleanup before sign-off.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2810,12 +2879,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equations justified for the physics; turbulence model selection rationale documented; known limitations stated.</t>
+          <t>Turbulence model selection justified for rotating-machinery application; known limitations documented; model assumptions stated</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>SST k-omega with curvature correction is a standard choice for rotating turbomachinery and is implicitly justified by practice. SAS and SA sensitivity runs provide some model-form evidence. Known limitations are partially documented (MRF steady-state limitations at off-design, omission of balance hole leakage, unsteady effects at surge). However, no formal model-form justification document is cited; the 7.4% head difference between SA and SST at 0.6 Q_BEP and 12% diffuser loss difference indicate unresolved model-form uncertainty at part-load.</t>
+          <t>SST k-ω with curvature correction is selected as the baseline, which is a reasonable choice for rotating machinery. SAS was tested at BEP. However, the 7.4% head discrepancy and 12% diffuser loss discrepancy between SST and S-A at 0.6 Q_BEP indicate significant model-form uncertainty at part-load that is not yet resolved. Leakage through balance holes is omitted without quantified impact. MRF vs sliding-mesh choice is partially explored (~2% torque difference) but not formally justified. Limitations are acknowledged qualitatively but not fully quantified.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2843,12 +2912,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties, geometry, and boundary conditions characterized with uncertainty; inputs traceable to measurements or vendor data.</t>
+          <t>Fluid properties matched to test conditions; geometry tolerance effects characterized; boundary conditions documented and justified</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Geometry from cleaned CAD; tip clearance set to 0.35 mm against drawing nominal 0.30±0.05 mm (within tolerance but at upper bound, not matched to test article measurement). Fluid properties set to 25 C water while test was at 30-32 C; viscosity not corrected in baseline runs (only a density correction applied in one sensitivity run). Inlet turbulence intensity sensitivity (3-10%) quantified. Rotational speed and geometry are well-defined. Input uncertainty is partially characterized but temperature/viscosity mismatch is a documented gap.</t>
+          <t>Tip clearance set to 0.35 mm against drawing tolerance of 0.30±0.05 mm; sensitivity not fully bounded. Fluid temperature mismatch is explicitly identified: CFD at 25 °C, test at 30–32 °C; viscosity correction was not applied (only density in one sensitivity run). Inlet turbulence intensity (5%) was varied in sensitivity study (3–10%). BC type inconsistency (mass-flow vs. fixed static pressure) was not logged. Input uncertainty is partially characterized but not consistently propagated.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2876,12 +2945,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Test article characterized; production-representative sample; sample size and geometric tolerance documented.</t>
+          <t>Test article characterization documented; sample representativeness established</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>The report references a vendor acceptance test but provides no information on the number of test runs, whether the test article is production-representative, or geometric tolerances of the physical pump as-tested. Tip clearance of the test article is not measured or reported. No statistical characterization of test-to-test repeatability is provided.</t>
+          <t>The vendor acceptance-test data is used as the experimental comparator but no information is provided in the report regarding the number of test runs, statistical characterization of the test data, production-representativeness of the test article, or test sample documentation. The report treats the test data as a single reference curve without characterization of test-to-test variability.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2902,19 +2971,19 @@
         </is>
       </c>
       <c r="C13" s="41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instruments; controlled environment; measurement uncertainty quantified; test standards referenced.</t>
+          <t>Test conditions (temperature, speed, fluid properties) documented; measurement uncertainty reported; calibrated instrumentation referenced</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>Test conducted at 30-32 C (fluid temperature reported); test head and efficiency values are quoted but measurement uncertainty is described only qualitatively as 4-5% on head (mentioned in the uncertainty discussion). No calibration records, test standards (e.g. ISO 9906), or instrument specifications are cited. The temperature range is reported but not controlled to a single point.</t>
+          <t>Test operating temperature (30–32 °C) and viscosity (0.75–0.80 mPa·s) are noted in the report, indicating some awareness of test conditions. Test head uncertainty is referenced as 4–5%. However, no detailed test protocol, instrument calibration records, or test standard (ASTM/ISO) references are provided. The temperature range reported (30–32 °C) is an approximate band, not a precisely controlled condition, and its impact on Reynolds number is flagged as a possible confound for off-BEP comparisons.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -2942,12 +3011,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Model inputs demonstrably matched to test conditions; differences quantified and their effect on QoIs assessed.</t>
+          <t>CFD inputs matched to test conditions; differences quantified and their effect on QoIs estimated</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Significant mismatches between model inputs and test conditions are documented and unresolved: fluid temperature 25 C in CFD vs 30-32 C in test (viscosity ~15-20% lower in test); boundary condition type changed for BEP calibration run but not logged; tip clearance in model (0.35 mm) not confirmed against as-tested geometry. The assessor explicitly states these inconsistencies must be resolved before the validation table is updated. No systematic propagation of input parameter differences to output uncertainty is completed.</t>
+          <t>Significant input parameter mismatches between the CFD model and the test are identified but not resolved: (1) fluid temperature 25 °C (CFD) vs 30–32 °C (test), with viscosity unadjusted in baseline runs; (2) BC type mismatch (fixed pressure used for BEP calibration without logging); (3) tip clearance nominal vs. drawing tolerance not fully reconciled. The report explicitly states the off-BEP comparison may be "apples-to-oranges" due to Reynolds number differences. These mismatches are unresolved at the time of this snapshot.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -2975,12 +3044,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative comparison of predictions to measurements with uncertainty bands; multiple QoIs and operating points; statistical validation metrics.</t>
+          <t>Quantitative error metrics reported for all QoIs at all operating points; uncertainty bands on predictions and measurements compared; consistent reporting across the operating map</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Quantitative comparisons are provided: head -1.1% and efficiency -0.8% at BEP; efficiency -6.5% and diffuser recovery 8-10% high at 0.6 Q_BEP. Combined uncertainty band ~3.2% on head at BEP is estimated. However, the "±3% everywhere" summary figure is explicitly flagged as unreliable due to double-counting of test uncertainty. Off-BEP comparisons are limited and confounded by temperature mismatch. No formal statistical validation metric (e.g. u-pooled, MAPE across all points) is computed. Multiple QoIs are partially compared but not systematically.</t>
+          <t>Quantitative head and efficiency errors are reported at BEP (–1.1%, –0.8%) and 0.6 Q_BEP (efficiency –6.5%; diffuser recovery 8–10% high). A combined uncertainty band (~3.2% on head at BEP from GCI + model spread) is estimated. However, the "±3% everywhere" claim is retracted by the author as internally inconsistent. Efficiency at 0.6 Q_BEP and diffuser recovery comparisons at multiple flow rates are incomplete. The output comparison is adequate at BEP but substantially weaker at off-design points.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3008,12 +3077,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs directly address the decision (trim guidance); measurable both computationally and experimentally.</t>
+          <t>QoIs (head, efficiency, diffuser pressure recovery) directly support trim decision-making and are measurable computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Head, efficiency, shaft power, and diffuser static pressure recovery are directly relevant to trim decisions for pump performance. These QoIs are computed by the CFD and measured in the acceptance test. The link between predicted head/efficiency trends and trim decision-making is clear. Qualitative flow features (tongue separation, swirl decay) are also noted as supportive QoIs. The QoIs are well-matched to the COU.</t>
+          <t>The QoIs — pump head, shaft efficiency, and diffuser static pressure recovery — directly correspond to the engineering decisions being made (impeller/diffuser trim selection near BEP). These quantities are computed by the CFD and measured in the vendor acceptance test. The linkage between the QoIs and the engineering decision (relative geometry ranking, BEP performance) is clearly stated. The limitation that stall-margin prediction is not yet a supported QoI is also explicitly documented.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3041,12 +3110,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions match COU operating conditions, geometry, physics regime, and fluid properties.</t>
+          <t>Validation conditions (geometry, speed, fluid, operating points) match the intended use; gaps explicitly identified and bounded</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation is performed on the same machine geometry and at the same nominal speed (2900 rpm), which is relevant. However, fluid temperature/viscosity mismatch (25 C CFD vs 30-32 C test) means Reynolds number differs, introducing a known physics-regime gap. The assessor explicitly notes the 0.6 Q_BEP comparison may be "apples-to-oranges" due to this. Steady-state MRF is validated but unsteady sliding-mesh (relevant to stall-margin COU) is not fully validated. The validation covers BEP adequately for the stated COU but coverage of off-BEP and stall-margin is insufficient.</t>
+          <t>The validation uses the actual P3-70 geometry at the intended operating speed (2900 rpm), which is directly relevant to the COU. BEP comparison is adequate. However, the COU also involves part-load behavior, and the off-BEP validation is compromised by fluid property mismatches, BC inconsistencies, and unresolved turbulence model sensitivity. The report explicitly limits the endorsed COU to BEP-centric trim decisions and flags part-load and stall-margin predictions as outside current validation coverage. This honest gap identification partially offsets the coverage weakness but does not close it.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3135,7 +3204,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The CFD model is accepted for the stated limited context of use — guiding impeller trim decisions near BEP — based on BEP head and efficiency predictions within approximately 1% of laboratory data and a combined uncertainty band of ~3.2% on head at BEP. Acceptance carries the following conditions documented by the assessor: (1) the model must NOT be used for stall-margin or off-BEP predictions until BC bookkeeping is corrected, fluid properties are matched to the rig temperature (30-32 C), near-wall treatment is made uniform on the fine mesh, and GCI is recomputed per quantity and operating point; (2) the "±3% everywhere" uncertainty claim must not be published until double-counting of test uncertainty is resolved; (3) turbulence model selection at 0.6 Q_BEP must be resolved (SA vs SST spread of 7.4% is unacceptable for design decisions at part-load); (4) case directories must be pushed to the cfd-p3 repository and config log updated to reflect the fixed-pressure BEP calibration BC.</t>
+          <t>The CFD model is accepted for the limited context of use of guiding BEP-centric impeller/diffuser trim decisions, where head error is –1.1% and combined GCI + turbulence-model uncertainty is approximately 3.2% — consistent with the stated accuracy need for relative geometry ranking. The assessor (A. Nguyen) explicitly endorses this limited use. Acceptance carries the following conditions recorded here: (1) the model is NOT accepted for stall-margin predictions or quantitative off-BEP (0.6 Q_BEP) performance claims until fluid properties are matched to test conditions, BC bookkeeping is corrected and logged, near-wall treatment is made consistent across all mesh levels, GCI is recomputed by quantity (head, torque, diffuser recovery) at all operating points, and turbulence-model spread at 0.6 Q_BEP is bounded to ≤3%; (2) the "±3% everywhere" uncertainty claim must be retracted and replaced with quantity- and operating-point-specific uncertainty statements; (3) case files must be pushed to the cfd-p3 repository with a valid link before any formal design release.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
